--- a/example_anova_table.xlsx
+++ b/example_anova_table.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\showalt_d\Documents\GitHub\Apiary_LRR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501D50F1-C2D0-4A5B-99F5-D95E1F40399F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83EF65F-2024-417D-ACF1-96FA9F38FC40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="3165" xr2:uid="{3AAE0910-517F-4774-AF8D-3B09DF664141}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ANOVA" sheetId="1" r:id="rId1"/>
+    <sheet name="lsmeans" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,14 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="17">
   <si>
     <t>Source</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>p</t>
   </si>
   <si>
@@ -48,9 +46,6 @@
     <t>Block</t>
   </si>
   <si>
-    <t>Treatment</t>
-  </si>
-  <si>
     <t>annual total mortality</t>
   </si>
   <si>
@@ -63,21 +58,61 @@
     <t>annual suppression mortality</t>
   </si>
   <si>
-    <t>EARLY (12+25)</t>
-  </si>
-  <si>
-    <t>MID (12+DF)</t>
-  </si>
-  <si>
-    <t>LATE (DF only)</t>
+    <t>Treatment (A,B,D,E)</t>
+  </si>
+  <si>
+    <t>Treatment (A,B,C)</t>
+  </si>
+  <si>
+    <t>EARLY</t>
+  </si>
+  <si>
+    <t>test statistic for random effect of block= LRT, fixed effect of treatment = F</t>
+  </si>
+  <si>
+    <t>Test stat.*</t>
+  </si>
+  <si>
+    <t>MIDDLE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (C only)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -134,16 +169,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,420 +494,392 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BF5774-CC3F-47FB-B6DB-43F70BC8900D}">
-  <dimension ref="B2:Q14"/>
+  <dimension ref="B2:Q16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" customWidth="1"/>
-    <col min="5" max="5" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="1.85546875" customWidth="1"/>
     <col min="7" max="7" width="4.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.28515625" customWidth="1"/>
     <col min="11" max="11" width="4.5703125" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="2.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="1.7109375" customWidth="1"/>
     <col min="15" max="15" width="4.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="3"/>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.29160000000000003</v>
       </c>
       <c r="G5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>4</v>
-      </c>
-      <c r="P5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>6.0979000000000001</v>
+      </c>
+      <c r="E6">
+        <v>7.9900000000000006E-3</v>
       </c>
       <c r="G6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
         <v>4</v>
       </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
       <c r="G7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -883,4 +891,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E239B243-56EB-4F4B-9694-8B3990C51D61}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>